--- a/data_extactor/batch_10_fa/batch_0069_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0069_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار ایمیل | IBM Notes | Infor ERP Baan | Infor XA | سیستم‌های مدیریت موجودی | نرم‌افزار موجودی | نرم‌افزار برنامه‌ریزی منابع مواد MRP | Microsoft Access | Microsoft Dynamics AX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Oracle Database | Oracle JD Edwards EnterpriseOne | نرم‌افزار تحلیل ریشه خطا | نرم‌افزار SAP | سیستم مدیریت انبار WMS</t>
+          <t>نرم‌افزار ایمیل | IBM Notes | Infor ERP Baan | Infor XA | سیستم‌های مدیریت موجودی | نرم‌افزار موجودی | نرم‌افزار برنامه‌ریزی منابع مواد MRP | Microsoft Access | Microsoft Dynamics AX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NetSuite ERP | Oracle Database | Oracle JD Edwards EnterpriseOne | نرم‌افزار تحلیل علت ریشه‌ای | نرم‌افزار SAP | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب خواندنی | سخن گفتن | پایش | گوش دادن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی | امور اداری و مدیریت | اداری</t>
+          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مشکل | درک مطلب کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | درک مطلب شفاهی | بیان شفاهی | استدلال قیاسی | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | بینایی دور | چالاکی انگشتان | سهولت کار با اعداد | استدلال ریاضی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | بینایی دور | مهارت انگشتان | توانایی عددی | استدلال ریاضی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان به صورت ایستاده | سرعت تعیین‌شده توسط سرعت تجهیزات | مکالمات تلفنی | داخل ساختمان، محیط کنترل‌شده از نظر دما | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | سرعت تعیین‌شده توسط سرعت تجهیزات | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | درجه‌بندی‌کنندگان و سورترهای محصولات کشاورزی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران و جابجا‌کنندگان دستی بار، انبار و مواد | کارگران خشکشویی و لباسشویی | درجه‌بندی‌کنندگان و اندازه‌گیران الوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کن | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندها و بسته‌بندی‌کنندگان دستی | سورترها، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش مرسولات اداره پست | کارمندان تولید، برنامه‌ریزی و تسریع امور | کارگران بازیافت و احیاء | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | کارمندان ارسال، دریافت و موجودی انبار | چیدمان‌کنندگان انبار و پرکنندگان سفارش | بارگیران واگن‌های مخزنی، کامیون‌ها و کشتی‌ها | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات</t>
+          <t>تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارکنان خشک‌شویی و لباس‌شویی | درجه‌بندی‌کنندگان و ارزیابان چوب | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارگران بازیافت و احیا | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | بارگیران واگن مخزنی، کامیون و کشتی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خواندنی | سخن گفتن | نوشتن | تفکر انتقادی | یادگیری فعال | پایش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>اداری | زبان انگلیسی | خدمات مشتریان و شخصی | کامپیوتر و الکترونیک | امور اداری و مدیریت</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | درک مطلب شفاهی | درک مطلب کتبی | بیان شفاهی | بیان کتبی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مشکل | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | اصالت | روانی ایده‌ها</t>
+          <t>تشخیص گفتار | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان به صورت نشسته | داخل ساختمان، محیط کنترل‌شده از نظر دما | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | فشار زمانی | اهمیت تکرار وظایف یکسان</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | کارمندان مکاتبات | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان خط مقدم کارگران سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | سرپرستان خط مقدم کارکنان پشتیبانی دفتری و اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتر، عمومی | دستیاران حقوقی و دستیاران قانون | متخصصان مدیریت پروژه | مدیران روابط عمومی | متخصصان روابط عمومی | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی</t>
+          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | کارمندان مکاتبات | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | پارالیگال‌ها و دستیاران حقوقی | متخصصان مدیریت پروژه | مدیران روابط عمومی | متخصصان روابط عمومی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A1-Law | ADP Workforce Now | AbacusNext HotDocs | Aderant CompuLaw | Adobe Acrobat | نرم‌افزار محاسبه استهلاک | نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار صدور فاکتور | نرم‌افزار مدیریت پرونده | Chrome River Expense | نرم‌افزار پایگاه داده | Dropbox | سیستم‌های مدیریت قضاوت الکترونیکی EAM | نرم‌افزار دفترچه یادداشت الکترونیکی | نرم‌افزار ایمیل | نرم‌افزار سیستم بایگانی | IBM Lotus Notes | Intuit QuickBooks | نرم‌افزار تحقیقات حقوقی | نرم‌افزار حقوقی | LexisNexis | LexisNexis Time Matters | نرم‌افزار مدیریت دعاوی حقوقی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | دسترسی عمومی به سوابق الکترونیکی دادگاه PACER | Quicken | Sage 50 Accounting | Thomson Reuters Elite Billing Manager | Thomson Reuters Westlaw | نرم‌افزار پیاده‌سازی گفتار | Vertican Technologies Collection Master | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | نرم‌افزار طراحی و ویرایش صفحات وب | WordPerfect</t>
+          <t>A1-Law | ADP Workforce Now | AbacusNext HotDocs | Aderant CompuLaw | Adobe Acrobat | نرم‌افزار محاسبه استهلاک | نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار صدور صورتحساب | نرم‌افزار مدیریت پرونده | Chrome River Expense | نرم‌افزار پایگاه داده | Dropbox | سیستم‌های مدیریت قضاوت الکترونیکی EAM | نرم‌افزار دفترچه یادداشت الکترونیکی | نرم‌افزار ایمیل | نرم‌افزار سیستم بایگانی | IBM Lotus Notes | Intuit QuickBooks | نرم‌افزار تحقیقات حقوقی | نرم‌افزار حقوقی | LexisNexis | LexisNexis Time Matters | نرم‌افزار مدیریت دعاوی حقوقی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Word | دسترسی عمومی به سوابق الکترونیکی دادگاه PACER | Quicken | Sage 50 Accounting | Thomson Reuters Elite Billing Manager | Thomson Reuters Westlaw | نرم‌افزار پیاده‌سازی گفتار | Vertican Technologies Collection Master | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | نرم‌افزار طراحی و ویرایش صفحه وب | WordPerfect</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خواندنی | نوشتن | سخن گفتن | پایش | تفکر انتقادی</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>اداری | زبان انگلیسی | قانون و حکومت | خدمات مشتریان و شخصی | کامپیوتر و الکترونیک | امور اداری و مدیریت | امنیت و ایمنی عمومی</t>
+          <t>اداری | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک مطلب شفاهی | درک مطلب کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مشکل</t>
+          <t>درک شفاهی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | صرف زمان به صورت نشسته | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان, محیط کنترل‌شده از نظر دما | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، دادرسان و ماموران رسیدگی | مدیران خدمات اداری | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و کپشن‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | کارمندان پردازش بیمه و بیمه‌نامه | کارمندان قضایی قانون | وکلا | متخصصان سوابق پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتر، عمومی | دستیاران حقوقی و دستیاران قانون | کارآگاهان و بازرسان خصوصی | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | مدیران خدمات اداری | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | کارمندان پردازش بیمه و بیمه‌نامه | کارمندان حقوقی قضایی | وکلا | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و بازرسان خصوصی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار حساب‌های پرداختنی | نرم‌افزار حساب‌های دریافتنی | نرم‌افزار آدرس‌دهی | Allscripts Payerpath | Allscripts Professional PM | Amazing Charts | نرم‌افزار صدور فاکتور | CPSI CPSI System | Corel WordPerfect Office Suite | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | Epic Systems | Google Docs | Google Drive | نرم‌افزار گرافیکی | HMS | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | IDX Groupcast | Intuit QuickBooks | Intuit QuickBooks Point of Sale | MEDENT | MEDITECH Medical and Practice Management MPM Suite | نرم‌افزار MEDITECH | McKesson Lytec | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | Microsys MicroMD | NaviMedix NaviNet | Patterson Dental Supply Patterson EagleSoft | PracticeWorks Systems Kodak WINOMS CS | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | Wisconsin Physicians Service Insurance CMS Secure Net Access Portal C-SNAP | dBASE Plus | eClinicalWorks EHR software | eMDs Medisoft</t>
+          <t>نرم‌افزار حساب‌های پرداختنی | نرم‌افزار حساب‌های دریافتنی | نرم‌افزار آدرس‌دهی | Allscripts Payerpath | Allscripts Professional PM | Amazing Charts | نرم‌افزار صدور صورتحساب | CPSI CPSI System | Corel WordPerfect Office Suite | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | Epic Systems | Google Docs | Google Drive | نرم‌افزار گرافیکی | HMS | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Henry Schein Dentrix | IDX Groupcast | Intuit QuickBooks | Intuit QuickBooks Point of Sale | MEDENT | MEDITECH Medical and Practice Management MPM Suite | نرم‌افزار MEDITECH | McKesson Lytec | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | Microsys MicroMD | NaviMedix NaviNet | Patterson Dental Supply Patterson EagleSoft | PracticeWorks Systems Kodak WINOMS CS | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب | Wisconsin Physicians Service Insurance CMS Secure Net Access Portal C-SNAP | dBASE Plus | نرم‌افزار eClinicalWorks EHR | eMDs Medisoft</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خواندنی | نوشتن | تفکر انتقادی | پایش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | پزشکی و دندانپزشکی | پرسنل و منابع انسانی | کامپیوتر و الکترونیک | امور اداری و مدیریت | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | پزشکی و دندان‌پزشکی | پرسنل و منابع انسانی | رایانه و الکترونیک | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک مطلب شفاهی | درک مطلب کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | حساسیت به مشکل</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | صرف زمان به صورت نشسته | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | داخل ساختمان، محیط کنترل‌شده از نظر دما | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعداد دفعات تصمیم‌گیری</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارمندان صدور فاکتور و ثبت | کارشناسان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | پزشکان طب اورژانس | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط مقدم کارکنان پشتیبانی دفتری و اداری | فناوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان، به جز واجد شرایط بودن و وام | دستیاران پزشکی | متخصصان سوابق پزشکی | پیاده‌سازان گفتار پزشکی | مدیران خدمات پزشکی و بهداشتی | کارمندان دفتر، عمومی | نمایندگان بیمار | تکنسین‌های داروخانه | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی</t>
+          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | پزشکان طب اورژانس | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | دستیاران پزشکی | متخصصان مدارک پزشکی | نسخه‌نویسان پزشکی | مدیران خدمات پزشکی و بهداشتی | کارمندان دفتری عمومی | نمایندگان بیمار | تکنسین‌های داروسازی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3M Post-it App | ADP Workforce Now | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Airtable | Apache Cassandra | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Pig | Apache Solr | Apache Tomcat | Apple Keynote | Apple macOS | نرم‌افزار زمان‌بندی قرار ملاقات | Atlassian Confluence | Atlassian JIRA | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Canva | Cisco Webex | نرم‌افزار رایانش ابری Citrix | ClassDojo | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار ورود داده | نرم‌افزار انبار داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار دیکته | Dropbox | Drupal | Evernote | FaceTime | Facebook | FileMaker Pro | نرم‌افزار سیستم بایگانی | نرم‌افزار حسابداری صندوق | Google Docs | Google Drive | Google Meet | Google Sheets | Google Sites | Google Slides | نرم‌افزار Google Workspace | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر دستی | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Maximo Asset Management | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IBM WebSphere | Intrado SchoolMessenger | Intuit QuickBooks | Kronos Workforce Timekeeper | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | McAfee | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | صفحات سرور فعال مایکروسافت ASP | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics SL | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Mozilla Firefox | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Qlik Tech QlikView | Quest Erwin Data Modeler | SAP Business Objects | SAP Concur | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | نرم‌افزار Salesforce | Schoology | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار ثبت زمان | Veritas NetBackup | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | نرم‌افزار Yardi | YouTube | Zoom | people@work</t>
+          <t>3M Post-it App | ADP Workforce Now | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Airtable | Apache Cassandra | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Pig | Apache Solr | Apache Tomcat | Apple Keynote | Apple macOS | نرم‌افزار زمان‌بندی قرار ملاقات | Atlassian Confluence | Atlassian JIRA | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Canva | Cisco Webex | نرم‌افزار رایانش ابری Citrix | ClassDojo | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار ورود داده | نرم‌افزار انبار داده | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار دیکته | Dropbox | Drupal | Evernote | FaceTime | Facebook | FileMaker Pro | نرم‌افزار سیستم بایگانی | نرم‌افزار حسابداری صندوق | Google Docs | Google Drive | Google Meet | Google Sheets | Google Sites | Google Slides | نرم‌افزار Google Workspace | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر جیبی | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM InfoSphere DataStage | IBM Maximo Asset Management | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | IBM WebSphere | Intrado SchoolMessenger | Intuit QuickBooks | Kronos Workforce Timekeeper | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | McAfee | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Dynamics SL | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows | Microsoft Word | Minitab | Mozilla Firefox | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Qlik Tech QlikView | Quest Erwin Data Modeler | SAP Business Objects | SAP Concur | SAP Crystal Reports | نرم‌افزار SAP | SAS | Sage 50 Accounting | نرم‌افزار Salesforce | Schoology | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار ثبت زمان | Veritas NetBackup | نرم‌افزار مرورگر وب | نرم‌افزار کنفرانس وب | نرم‌افزار Yardi | YouTube | Zoom | people@work</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خواندنی | نوشتن | پایش | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>اداری | زبان انگلیسی | کامپیوتر و الکترونیک | خدمات مشتریان و شخصی | امور اداری و مدیریت</t>
+          <t>اداری | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک مطلب شفاهی | درک مطلب کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مشکل | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | اهمیت تکرار وظایف یکسان | تعیین وظایف, اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | فشار زمانی | داخل ساختمان، محیط کنترل‌شده از نظر دما | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | کارمندان مکاتبات | کارمندان دادگاه، شهرداری و مجوز | کارشناسان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | سرپرستان خط مقدم کارکنان پشتیبانی دفتری و اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | مصاحبه‌کنندگان، به جز واجد شرایط بودن و وام | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتر، عمومی | پذیرش‌کنندگان و کارمندان اطلاعات | دستیاران پژوهشی علوم اجتماعی | اپراتورهای تلفنخانه، شامل خدمات پاسخگویی</t>
+          <t>مدیران خدمات اداری | مدیران ارشد اجرایی | کارمندان مکاتبات | کارمندان دادگاه، شهرداری و مجوز | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | متصدیان پذیرش و کارمندان اطلاعات | دستیاران تحقیقات علوم اجتماعی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Blackbaud The Raiser's Edge | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک پزشکی EMR | FaceTime | FileMaker Pro | Google Docs | Google Drive | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | IBM Informix | Intuit QuickBooks | Jenzabar ERP | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Perceptive Software Intelligent Capture | نرم‌افزار SAP | Sage 50 Accounting | Salesforce.com Salesforce CRM</t>
+          <t>Blackbaud The Raiser's Edge | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | FaceTime | FileMaker Pro | Google Docs | Google Drive | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | IBM Informix | Intuit QuickBooks | Jenzabar ERP | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Perceptive Software Intelligent Capture | نرم‌افزار SAP | Sage 50 Accounting | Salesforce.com Salesforce CRM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | گوش دادن فعال | پایش | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اداری | خدمات مشتریان و شخصی | قانون و حکومت</t>
+          <t>زبان انگلیسی | اداری | خدمات مشتری و شخصی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک مطلب کتبی | بینایی نزدیک | چالاکی انگشتان | ترتیب‌دهی اطلاعات | درک مطلب شفاهی | تشخیص گفتار | سرعت ادراکی | توجه انتخابی | وضوح گفتار | سرعت مچ و انگشت | انعطاف‌پذیری دسته‌بندی | بیان کتبی | استدلال استقرایی | بیان شفاهی</t>
+          <t>درک کتبی | بینایی نزدیک | مهارت انگشتان | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص گفتار | سرعت ادراکی | توجه انتخابی | وضوح گفتار | سرعت مچ و انگشتان | انعطاف‌پذیری دسته‌بندی | بیان کتبی | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت نشسته | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فشار زمانی | مکالمات تلفنی | داخل ساختمان، محیط کنترل‌شده از نظر دما | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | فشار زمانی | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارمندان صدور فاکتور و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | فناوران و تکنسین‌های کالیبراسیون | کارمندان مکاتبات | متخصصان مدیریت اسناد | کارمندان بایگانی | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | متخصصان سوابق پزشکی | کارمندان دفتر، عمومی | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | کارمندان حقوق و دستمزد و ثبت زمان | سورترها، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش مرسولات اداره پست | کارمندان تولید، برنامه‌ریزی و تسریع امور | غلط‌گیران و نشانه‌گذاران کپی | کارمندان ارسال، دریافت و موجودی انبار | دستیاران آماری | اپراتورهای تلفنخانه، شامل خدمات پاسخگویی | ارزیابان سند، خلاصه‌نویسان و جستجوگران سند | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | واژه‌پردازان و تایپیست‌ها</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | کارمندان مکاتبات | متخصصان مدیریت اسناد | کارمندان بایگانی | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | متخصصان مدارک پزشکی | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | کارمندان حقوق و دستمزد و ثبت زمان | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | کارمندان تولید، برنامه‌ریزی و هماهنگی | مصححان و نشانه‌گذاران کپی | کارمندان ارسال، دریافت و موجودی کالا | دستیاران آماری | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | نوشتن | گوش دادن فعال | پایش | سخن گفتن</t>
+          <t>درک مطلب | نگارش | گوش دادن فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>اداری | زبان انگلیسی | خدمات مشتریان و شخصی | کامپیوتر و الکترونیک</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک مطلب کتبی | تشخیص گفتار | درک مطلب شفاهی | بیان کتبی | سرعت مچ و انگشت | ترتیب‌دهی اطلاعات | بیان شفاهی | وضوح گفتار | چالاکی انگشتان | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
+          <t>بینایی نزدیک | درک کتبی | تشخیص گفتار | درک شفاهی | بیان کتبی | سرعت مچ و انگشتان | ترتیب‌دهی اطلاعات | بیان شفاهی | وضوح گفتار | مهارت انگشتان | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | صرف زمان به صورت نشسته | ایمیل | ارتباط با دیگران | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | داخل ساختمان، محیط کنترل‌شده از نظر دما | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری</t>
+          <t>مکالمات تلفنی | صرف زمان برای نشستن | ایمیل | ارتباط با دیگران | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارمندان صدور فاکتور و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان مکاتبات | گزارشگران دادگاه و کپشن‌نویسان همزمان | اپراتورهای ورود داده | متخصصان مدیریت اسناد | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | منشی‌های حقوقی و دستیاران اداری | متخصصان سوابق پزشکی | منشی‌های پزشکی و دستیاران اداری | پیاده‌سازان گفتار پزشکی | کارمندان دفتر، عمومی | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | غلط‌گیران و نشانه‌گذاران کپی | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری | اپراتورهای تلفنخانه، شامل خدمات پاسخگویی | ارزیابان سند، خلاصه‌نویسان و جستجوگران سند</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | اپراتورهای ورود داده | متخصصان مدیریت اسناد | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | منشی‌های حقوقی و دستیاران اداری | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | نسخه‌نویسان پزشکی | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | مصححان و نشانه‌گذاران کپی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AT&amp;T Troff | Actuate DocBook | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe LiveMotion | Adobe PageMaker | Adobe Photoshop | Adobe PostScript | AlgoLab Raster to Vector Conversion Toolkit | Apple AppleScript | Apple iPhoto | Apple macOS | Arts &amp; Letters Express | برگه‌های سبک آبشاری CSS | Cenon | CodedColor | نرم‌افزار مدیریت رنگ | Corel CorelDraw Graphics Suite | Corel CorelScan | Corel OCR-Trace 8 | Corel Paint Shop Pro | Corel Photo-Paint | Corel Ventura | Corel WebDraw | Corel WordPerfect Office Suite | EMC Documentum | زبان نشانه‌گذاری گسترش‌پذیر XML | Finite Matters PatternStream | GNU Image Manipulation Program GIMP | GTX RastorCAD | نرم‌افزار گرافیکی | GrassHopper PageStream | زبان نشانه‌گذاری ابرمتن HTML | Inkscape | JavaScript | LaTeX | نرم‌افزار نقشه‌برداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Picture It! | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | MySQL | Nuance Dragon NaturallySpeaking | Nuance OmniPage Professional | Objectif Lune PlanetPress Suite | نرم‌افزار پایگاه داده تصویر و گرافیک آنلاین | OpenOffice.org | Oracle Java | PANTONE ColorVision ProfilerPlus | PHP | Perl | نرم‌افزار ساخت فایل سند قابل حمل | Potrace | Python | QuarkXPress | ویرایشگرهای گرافیک شطرنجی | نرم‌افزار SAP | نرم‌افزار Salesforce | گرافیک برداری مقیاس‌پذیر SVG | Scribus | Serif PagePlus | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار بررسی املا و دستور زبان | Sun Microsystems Java | Trix TracTrix | UNIX | Ulead PhotoImpact | نرم‌افزار ترسیم برداری | نرم‌افزار شبکه خصوصی مجازی VPN | WordWeb | Xara Designer Pro | jQuery</t>
+          <t>AT&amp;T Troff | Actuate DocBook | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe FrameMaker | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe LiveMotion | Adobe PageMaker | Adobe Photoshop | Adobe PostScript | AlgoLab Raster to Vector Conversion Toolkit | Apple AppleScript | Apple iPhoto | Apple macOS | Arts &amp; Letters Express | برگه‌های سبک آبشاری CSS | Cenon | CodedColor | نرم‌افزار مدیریت رنگ | Corel CorelDraw Graphics Suite | Corel CorelScan | Corel OCR-Trace 8 | Corel Paint Shop Pro | Corel Photo-Paint | Corel Ventura | Corel WebDraw | Corel WordPerfect Office Suite | EMC Documentum | زبان نشانه‌گذاری توسعه‌پذیر XML | Finite Matters PatternStream | برنامه دستکاری تصویر گنو GIMP | GTX RastorCAD | نرم‌افزار گرافیکی | GrassHopper PageStream | زبان نشانه‌گذاری ابرمتن HTML | Inkscape | JavaScript | LaTeX | نرم‌افزار نقشه‌برداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Picture It! | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | MySQL | Nuance Dragon NaturallySpeaking | Nuance OmniPage Professional | Objectif Lune PlanetPress Suite | نرم‌افزار پایگاه داده تصویر و گرافیک آنلاین | OpenOffice.org | Oracle Java | PANTONE ColorVision ProfilerPlus | PHP | Perl | نرم‌افزار ساخت فایل سند قابل حمل | Potrace | Python | QuarkXPress | ویرایشگرهای گرافیک شطرنجی | نرم‌افزار SAP | نرم‌افزار Salesforce | گرافیک برداری مقیاس‌پذیر SVG | Scribus | Serif PagePlus | نرم‌افزار رسانه‌های اجتماعی | نرم‌افزار بررسی املا و دستور زبان | Sun Microsystems Java | Trix TracTrix | UNIX | Ulead PhotoImpact | نرم‌افزار ترسیم برداری | نرم‌افزار شبکه خصوصی مجازی VPN | WordWeb | Xara Designer Pro | jQuery</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نوشتن | پایش | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | تجسم | درک مطلب کتبی | روانی ایده‌ها | درک مطلب شفاهی | بیان کتبی | حساسیت به مشکل | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ‌های بصری | سرعت ادراکی | استدلال قیاسی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | بینایی دور | استدلال استقرایی | انعطاف‌پذیری بستار</t>
+          <t>بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | تجسم | درک کتبی | روانی ایده‌ها | درک شفاهی | بیان کتبی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | سرعت ادراکی | استدلال قیاسی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | بینایی دور | استدلال استقرایی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | داخل ساختمان، محیط کنترل‌شده از نظر دما | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت نشسته | فشار زمانی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | فشار زمانی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران هنری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | اپراتورهای ورود داده | متخصصان مدیریت اسناد | ویراستاران | کارمندان بایگانی | تدوین‌گران فیلم و ویدئو | طراحان گرافیک | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های پردازش | تکنسین‌ها و کارگران پیش‌چاپ | غلط‌گیران و نشانه‌گذاران کپی | توسعه‌دهندگان نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | نویسندگان فنی | طراحان بازی‌های ویدئویی | مدیران وب | توسعه‌دهندگان وب | طراحان رابط کاربری وب و دیجیتال</t>
+          <t>مدیران هنری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | اپراتورهای ورود داده | متخصصان مدیریت اسناد | ویراستاران | کارمندان بایگانی | تدوینگران فیلم و ویدئو | طراحان گرافیک | اپراتورهای ماشین‌های اداری، به جز رایانه | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | تکنسین‌ها و کارگران پیش از چاپ | مصححان و نشانه‌گذاران کپی | توسعه‌دهندگان نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | نویسندگان فنی | طراحان بازی‌های ویدئویی | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت حساب | Alpha Software Alpha Five | نرم‌افزار سیستم اطلاعات خودکار | نرم‌افزار صدور فاکتور | نرم‌افزار سیستم پردازش خسارت | نرم‌افزار پایگاه داده | GroupMe | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | IBM Check Processing Control System CPSC | IBM Lotus Notes | InSystems Calligo Enterprise | نرم‌افزار نرخ‌گذاری بیمه | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroFocus GroupWise | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار سیستم صدور بیمه‌نامه | St. Paul Travelers e-CARMA | نرم‌افزار مرورگر وب | Xactware Xactimate</t>
+          <t>نرم‌افزار مدیریت حساب | Alpha Software Alpha Five | نرم‌افزار سیستم اطلاعات خودکار | نرم‌افزار صدور صورتحساب | نرم‌افزار سیستم پردازش خسارت | نرم‌افزار پایگاه داده | GroupMe | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | IBM Check Processing Control System CPSC | IBM Lotus Notes | InSystems Calligo Enterprise | نرم‌افزار نرخ‌گذاری بیمه | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroFocus GroupWise | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار سیستم صدور بیمه‌نامه | St. Paul Travelers e-CARMA | نرم‌افزار مرورگر وب | Xactware Xactimate</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب خواندنی | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نوشتن | پایش</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | اداری | زبان انگلیسی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک مطلب شفاهی | درک مطلب کتبی | وضوح گفتار | تشخیص گفتار | بیان شفاهی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مشکل | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | بیان شفاهی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | مکالمات تلفنی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | داخل ساختمان، محیط کنترل‌شده از نظر دما | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعداد دفعات تصمیم‌گیری | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی</t>
+          <t>ایمیل | صرف زمان برای نشستن | مکالمات تلفنی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>وصول‌کنندگان قبض و حساب | کارمندان صدور فاکتور و ثبت | کارمندان دفترداری, حسابداری و حسابرسی | کارمندان کارگزاری | ارزیابان، ممتحنان و بازرسان خسارت | متخصصان جبران خدمات، مزایا و تجزیه و تحلیل شغل | کارمندان مکاتبات | صادرکنندگان مجوز اعتبار، کنترل‌کنندگان و کارمندان اعتبار | کارشناسان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان فروش بیمه | پذیره‌نویسان بیمه | منشی‌های حقوقی و دستیاران اداری | مصاحبه‌کنندگان و کارمندان وام | متخصصان سوابق پزشکی | کارمندان حساب‌های جدید | کارمندان دفتر، عمومی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | ممیزان و وصول‌کنندگان مالیات، و ماموران درآمد | ارزیابان سند، خلاصه‌نویسان و جستجوگران سند</t>
+          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | متخصصان جبران خدمات، مزایا و تحلیل شغل | کارمندان مکاتبات | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | نمایندگان فروش بیمه | بیمه‌گران | منشی‌های حقوقی و دستیاران اداری | مصاحبه‌کنندگان و کارمندان وام | متخصصان مدارک پزشکی | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | سخن گفتن | درک مطلب خواندنی</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک مطلب شفاهی | درک مطلب کتبی | تشخیص گفتار | چالاکی انگشتان | چالاکی دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | ثبات بازو-دست | استدلال قیاسی | حساسیت به مشکل | بیان شفاهی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | تشخیص گفتار | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده از نظر دما | مکالمات تلفنی | ایمیل | تعداد دفعات تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | صرف زمان به صورت ایستاده | پیامدهای کاری و نتایج سایر کارگران | نامه‌ها و یادداشت‌های کتبی | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | ایمیل | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | صرف زمان برای ایستادن | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نمایندگان بار و کارگو | صندوقداران | پیک‌ها و نامه‌رسان‌ها | اپراتورهای ورود داده | کارمندان بایگانی | کارگران و جابجا‌کنندگان دستی بار، انبار و مواد | رانندگان کامیون‌های سبک | کارمندان دفتر، عمومی | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | کارمندان سفارشات | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کارمندان اداره پست | نامه‌رسان‌های اداره پست | سورترها، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش مرسولات اداره پست | روسای پست و ناظران پست | پذیرش‌کنندگان و کارمندان اطلاعات | کارمندان ارسال، دریافت و موجودی انبار | چیدمان‌کنندگان انبار و پرکنندگان سفارش | اپراتورهای تلفنخانه، شامل خدمات پاسخگویی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
+          <t>نمایندگان بار و محموله | صندوق‌داران | پیک‌ها و نامه‌رسان‌ها | اپراتورهای ورود داده | کارمندان بایگانی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | رانندگان کامیون‌های سبک | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | کارمندان ثبت سفارش | بسته‌بندهای دستی | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | رئیس پست و سرپرستان پست | متصدیان پذیرش و کارمندان اطلاعات | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0069_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0069_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>تولید و فرآوری | ریاضیات | زبان انگلیسی | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | سرعت ادراک | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری در بستن الگوها | وضوح گفتار | دید دور | چابکی انگشتان | مهارت در محاسبات عددی | استدلال ریاضی | استدلال استقرایی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک کتبی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت ادراکی | توجه انتخابی | درک شفاهی | بیان شفاهی | استدلال قیاسی | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | وضوح گفتار | بینایی دور | مهارت انگشتان | توانایی عددی | استدلال ریاضی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌شکن، آسیاب و پرداخت‌کاری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، قالب‌گیری، پرس و تراکم‌سازی | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | بازرسان، آزمون‌گران، سورت‌کنندگان، نمونه‌برداران و توزین‌کنندگان | کارگران ساده و جابه‌جا‌کنندگان دستی بار، کالا و مواد | کارگران خشکشویی و رختشویخانه | درجه‌بندی‌کنندگان و اندازه‌گیران الوار و چوب | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات تولیدی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | بسته‌بندها و کارگران بسته‌بندی دستی | سورت‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌آلات تفکیک مرسولات پستی | کارمندان برنامه‌ریزی، کنترل تولید و پیگیری سفارش‌ها | کارگران بازیافت و احیای مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌گیری و تقطیر | کارمندان انبار، ورود و خروج کالا و موجودی | متصدیان چیدمان و جمع‌آوری سفارش‌ها در انبار | بارگیران مخازن ریلی، کامیونی و کشتی | اپراتورها و متصدیان ماشین‌های رنگرزی و سفیدگری منسوجات</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشکشویی و رختشویخانه | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | اپراتورها و متصدیان تفکیک و پردازش پستی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارگران بازیافت و تفکیک پسماند | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | دید نزدیک | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | سرعت ادراک | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی | توجه انتخابی | انعطاف‌پذیری در بستن الگوها | استدلال استقرایی | ابتکار | روانی ایده‌ها</t>
+          <t>تشخیص گفتار | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | بینایی نزدیک | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | مدیران ارشد اجرایی | کارمندان امور مکاتبات اداری | کارشناسان پذیرش و بررسی واجدین شرایط برنامه‌های دولتی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به جز مراکز بازی | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | دستیاران منابع انسانی، به جز امور حقوق و دستمزد و ثبت زمان کار | کارشناسان منابع انسانی | منشی‌ها و مسئولان دفاتر حقوقی | تحلیل‌گران مدیریت و بهبود فرآیندها | منشی‌ها و مسئولان دفاتر پزشکی و درمانی | کارمندان امور دفتری و عمومی | کارشناسان حقوقی و دستیاران وکالت | کارشناسان مدیریت پروژه | مدیران روابط عمومی | کارشناسان روابط عمومی | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی | منشی‌ها و دستیاران اداری، به جز حوزه‌های حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان و دستیاران امور حقوقی | کارشناسان مدیریت پروژه | مدیران روابط عمومی | کارشناسان روابط عمومی | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | سخن گفتن | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | حقوق و امور دولتی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | ایمنی و امنیت عمومی</t>
+          <t>اداری | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | دید نزدیک | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بینایی نزدیک | بیان شفاهی | بیان کتبی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دادیاران، کارشناسان رسیدگی و مستشاران اداری | مدیران خدمات اداری و پشتیبانی | کارشناسان انطباق با مقررات و بازرسی | کارمندان امور مکاتبات اداری | تندنویسان و ثبت‌کنندگان جلسات دادگاه و زیرنویس‌نویسان هم‌زمان | کارمندان دبیرخانه مراجع قضایی و صدور مجوز | کارشناسان پذیرش و بررسی واجدین شرایط برنامه‌های دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی و ثبت اسناد | دستیاران منابع انسانی، به جز امور حقوق و دستمزد و ثبت زمان کار | کارمندان پردازش خسارت و بیمه‌نامه‌ها | دستیاران پژوهشی قضایی و دفتریاران دادگاه | وکلا و مشاوران حقوقی | کارشناسان اسناد و مدارک پزشکی | منشی‌ها و مسئولان دفاتر پزشکی و درمانی | کارمندان امور دفتری و عمومی | کارشناسان حقوقی و دستیاران وکالت | کارآگاهان خصوصی و بازرسان کشف جرایم | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی | منشی‌ها و دستیاران اداری، به جز حوزه‌های حقوقی، پزشکی و اجرایی</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مدیران خدمات اداری و پشتیبانی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان پژوهش و تحریر قضایی | وکلا | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان و دستیاران امور حقوقی | کارآگاهان و بازرسان خصوصی | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | پزشکی و دندانپزشکی | امور کارکنان و منابع انسانی | رایانه و الکترونیک | مدیریت و امور اداری | علوم اقتصادی و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | پزشکی و دندان‌پزشکی | پرسنل و منابع انسانی | رایانه و الکترونیک | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | کارمندان صدور صورت‌حساب و محاسبات مالی | کارشناسان خدمات مشتریان | کارشناسان پذیرش و بررسی واجدین شرایط برنامه‌های دولتی | پزشکان طب اورژانس | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | کارشناسان فناوری اطلاعات سلامت و ثبت‌کنندگان اسناد پزشکی | دستیاران منابع انسانی، به جز امور حقوق و دستمزد و ثبت زمان کار | کارمندان پردازش خسارت و بیمه‌نامه‌ها | متصدیان مصاحبه و ثبت اطلاعات، به جز حوزه‌های احراز صلاحیت و تسهیلات | دستیاران پزشک | کارشناسان اسناد و مدارک پزشکی | پیاده‌سازان متون و گزارش‌های پزشکی | مدیران خدمات بهداشتی و درمانی | کارمندان امور دفتری و عمومی | نمایندگان پیگیری حقوق بیماران | تکنسین‌های داروخانه | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی | منشی‌ها و دستیاران اداری، به جز حوزه‌های حقوقی، پزشکی و اجرایی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | پزشکان طب اورژانس | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارمندان پردازش خسارت و بیمه‌نامه‌ها | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کمک‌پزشکان و دستیاران مطب | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | پیاده‌سازان و تایپیست‌های متون پزشکی | مدیران خدمات درمانی و بهداشتی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان امور بیماران و پذیرش | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>اداری | زبان انگلیسی | رایانه و الکترونیک | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>بیان کتبی | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | مدیران ارشد اجرایی | کارمندان امور مکاتبات اداری | کارمندان دبیرخانه مراجع قضایی و صدور مجوز | کارشناسان خدمات مشتریان | کارشناسان پذیرش و بررسی واجدین شرایط برنامه‌های دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی و ثبت اسناد | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور اداری و پشتیبانی دفتری | دستیاران منابع انسانی، به جز امور حقوق و دستمزد و ثبت زمان کار | کارشناسان منابع انسانی | متصدیان مصاحبه و ثبت اطلاعات، به جز حوزه‌های احراز صلاحیت و تسهیلات | منشی‌ها و مسئولان دفاتر حقوقی | تحلیل‌گران مدیریت و بهبود فرآیندها | منشی‌ها و مسئولان دفاتر پزشکی و درمانی | کارمندان امور دفتری و عمومی | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی | دستیاران پژوهشی علوم اجتماعی | متصدیان تلفن‌خانه و پاسخگویی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران عامل و مدیران ارشد اجرایی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | اپراتورهای مراکز تلفن و پاسخگویی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امور اداری و دفتری | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی</t>
+          <t>زبان انگلیسی | اداری | خدمات مشتری و شخصی | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | چابکی انگشتان | مرتب‌سازی اطلاعات | درک شفاهی | تشخیص گفتار | سرعت ادراک | توجه انتخابی | وضوح گفتار | سرعت حرکت مچ و انگشتان دست | انعطاف‌پذیری در دسته‌بندی | بیان کتبی | استدلال استقرایی | بیان شفاهی</t>
+          <t>درک کتبی | بینایی نزدیک | مهارت انگشتان | ترتیب‌دهی اطلاعات | درک شفاهی | تشخیص گفتار | سرعت ادراکی | توجه انتخابی | وضوح گفتار | سرعت مچ و انگشتان | انعطاف‌پذیری دسته‌بندی | بیان کتبی | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و محاسبات مالی | کارمندان حسابداری و حسابرسی | کارشناسان و تکنسین‌های کالیبراسیون | کارمندان امور مکاتبات اداری | کارشناسان مدیریت اسناد و مدارک | کارمندان بایگانی و ثبت اسناد | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | کارشناسان اسناد و مدارک پزشکی | کارمندان امور دفتری و عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | کارمندان امور حقوق و دستمزد و ثبت زمان کار | سورت‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌آلات تفکیک مرسولات پستی | کارمندان برنامه‌ریزی، کنترل تولید و پیگیری سفارش‌ها | نمونه‌خوانان و غلط‌گیران متون چاپی | کارمندان انبار، ورود و خروج کالا و موجودی | دستیاران آمار | متصدیان تلفن‌خانه و پاسخگویی | بازبینان، خلاصه‌نویسان و جست‌وجوگران اسناد ملکی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | کارشناسان تایپ و حروف‌چینی دیجیتال</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | کارمندان امور حقوق، دستمزد و ثبت زمان | اپراتورها و متصدیان تفکیک و پردازش پستی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | ویراستاران فنی و نمونه‌خوان‌ها | کارمندان انبار، ارسال و دریافت کالا | دستیاران و تکنسین‌های آمار | اپراتورهای مراکز تلفن و پاسخگویی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | شنیدن فعال | نظارت | سخن گفتن</t>
+          <t>درک مطلب | نگارش | گوش دادن فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | تشخیص گفتار | درک شفاهی | بیان کتبی | سرعت حرکت مچ و انگشتان دست | مرتب‌سازی اطلاعات | بیان شفاهی | وضوح گفتار | چابکی انگشتان | سرعت ادراک | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی</t>
+          <t>بینایی نزدیک | درک کتبی | تشخیص گفتار | درک شفاهی | بیان کتبی | سرعت مچ و انگشتان | ترتیب‌دهی اطلاعات | بیان شفاهی | وضوح گفتار | مهارت انگشتان | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورت‌حساب و محاسبات مالی | کارمندان حسابداری و حسابرسی | کارمندان امور مکاتبات اداری | تندنویسان و ثبت‌کنندگان جلسات دادگاه و زیرنویس‌نویسان هم‌زمان | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | کارمندان بایگانی و ثبت اسناد | منشی‌ها و مسئولان دفاتر حقوقی | کارشناسان اسناد و مدارک پزشکی | منشی‌ها و مسئولان دفاتر پزشکی و درمانی | پیاده‌سازان متون و گزارش‌های پزشکی | کارمندان امور دفتری و عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | نمونه‌خوانان و غلط‌گیران متون چاپی | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی | منشی‌ها و دستیاران اداری، به جز حوزه‌های حقوقی، پزشکی و اجرایی | دستیاران آمار | متصدیان تلفن‌خانه و پاسخگویی | بازبینان، خلاصه‌نویسان و جست‌وجوگران اسناد ملکی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | پیاده‌سازان و تایپیست‌های متون پزشکی | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | ویراستاران فنی و نمونه‌خوان‌ها | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | دستیاران و تکنسین‌های آمار | اپراتورهای مراکز تلفن و پاسخگویی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | مرتب‌سازی اطلاعات | ابتکار | تجسم فضایی | درک کتبی | روانی ایده‌ها | درک شفاهی | بیان کتبی | حساسیت به مسئله | انعطاف‌پذیری در دسته‌بندی | تشخیص رنگ‌های بصری | سرعت ادراک | استدلال قیاسی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | دید دور | استدلال استقرایی | انعطاف‌پذیری در بستن الگوها</t>
+          <t>بینایی نزدیک | ترتیب‌دهی اطلاعات | اصالت | تجسم | درک کتبی | روانی ایده‌ها | درک شفاهی | بیان کتبی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | تشخیص رنگ بصری | سرعت ادراکی | استدلال قیاسی | بیان شفاهی | توجه انتخابی | وضوح گفتار | تشخیص گفتار | بینایی دور | استدلال استقرایی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران هنری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | ویراستاران | کارمندان بایگانی و ثبت اسناد | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | اپراتورهای ماشین‌های اداری، به جز رایانه | کارگران و اپراتورهای پردازش عکس و لابراتوار | تکنسین‌ها و کارگران لیتوگرافی و پیش‌ازچاپ | نمونه‌خوانان و غلط‌گیران متون چاپی | توسعه‌دهندگان نرم‌افزار | طراحان انیمیشن و جلوه‌های ویژه | نویسندگان فنی و کارشناسان نگارش متون تخصصی | طراحان بازی‌های ویدئویی | مدیران سایت و وب‌مسترها | توسعه‌دهندگان وب | طراحان وب و رابط کاربری دیجیتال</t>
+          <t>مدیران هنری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | ویراستاران | متصدیان بایگانی و اسناد | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | ویراستاران فنی و نمونه‌خوان‌ها | توسعه‌دهندگان نرم‌افزار | پویانماها و طراحان جلوه‌های ویژه | نویسندگان متون فنی | طراحان بازی‌های ویدیویی | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری و دفتری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | بیان شفاهی | دید نزدیک | بیان کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی</t>
+          <t>درک شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | بیان شفاهی | بینایی نزدیک | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان وصول مطالبات و بدهی‌ها | کارمندان صدور صورت‌حساب و محاسبات مالی | کارمندان حسابداری و حسابرسی | کارمندان کارگزاری‌های مالی و بیمه‌ای | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارمندان امور مکاتبات اداری | کارمندان اعتبارسنجی و تأیید اعتبارات مالی | کارشناسان خدمات مشتریان | کارشناسان پذیرش و بررسی واجدین شرایط برنامه‌های دولتی | نمایندگان و کارشناسان فروش بیمه | پذیره‌نویسان و کارشناسان صدور بیمه | منشی‌ها و مسئولان دفاتر حقوقی | متصدیان مصاحبه و ثبت درخواست وام و تسهیلات | کارشناسان اسناد و مدارک پزشکی | کارمندان افتتاح حساب و خدمات مشتریان | کارمندان امور دفتری و عمومی | کارشناسان فروش خدمات | ممیزان و وصول‌کنندگان مالیات و مأموران امور مالیاتی | بازبینان، خلاصه‌نویسان و جست‌وجوگران اسناد ملکی</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | تشخیص گفتار | چابکی انگشتان | چابکی دستی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | ثبات دست و بازو | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | تشخیص گفتار | مهارت انگشتان | مهارت دستی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان پذیرش بار و کارگو | صندوق‌داران | پیک‌ها و نامه‌رسانان | متصدیان ورود اطلاعات و داده‌آمایی | کارمندان بایگانی و ثبت اسناد | کارگران ساده و جابه‌جا‌کنندگان دستی بار، کالا و مواد | رانندگان خودروهای باری سبک و وانت | کارمندان امور دفتری و عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | کارمندان ثبت و پیگیری سفارش‌ها | بسته‌بندها و کارگران بسته‌بندی دستی | متصدیان باجه‌های پستی | مأموران توزیع مرسولات و نامه‌رسانان دولتی | سورت‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌آلات تفکیک مرسولات پستی | مدیران و سرپرستان دفاتر و مراکز توزیع پستی | متصدیان پذیرش و کارمندان اطلاعات و راهنمایی | کارمندان انبار، ورود و خروج کالا و موجودی | متصدیان چیدمان و جمع‌آوری سفارش‌ها در انبار | متصدیان تلفن‌خانه و پاسخگویی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
+          <t>کارگزاران حمل‌ونقل و بار | صندوق‌داران | پیک‌ها و نامه‌رسان‌ها | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان بایگانی و اسناد | کارگران جابه‌جایی دستی بار، کالا و مصالح | رانندگان خودروهای باربری سبک و وانت‌بارها | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | متصدیان ثبت و پیگیری سفارش‌ها | کارگران بسته‌بندی دستی | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | مدیران و رؤسای دفاتر پستی | متصدیان پذیرش و اطلاعات | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | اپراتورهای مراکز تلفن و پاسخگویی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
